--- a/data/trans_orig/IP74A2_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP74A2_2023-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Adulto según si ha resuelto el alquiler en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Adultos según si tienen resuelto el retraso en los pagos del alquiler en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -765,7 +765,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>240</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -780,7 +780,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -800,7 +800,7 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>232</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
@@ -815,7 +815,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1992</t>
+          <t>2232</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,27%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2394</t>
+          <t>2648</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,39%</t>
+          <t>100,0%</t>
         </is>
       </c>
     </row>
@@ -1148,7 +1148,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2401</t>
+          <t>2461</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>74,37%</t>
+          <t>76,24%</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>805</t>
+          <t>772</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1271,7 +1271,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -2285,7 +2285,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>893</t>
+          <t>547</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -2300,7 +2300,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>43,06%</t>
+          <t>26,4%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2445,7 +2445,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>574</t>
+          <t>716</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -2460,7 +2460,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>26,38%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>698</t>
+          <t>704</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4172</t>
+          <t>4175</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>83,44%</t>
+          <t>83,5%</t>
         </is>
       </c>
     </row>
@@ -2563,7 +2563,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2130</t>
+          <t>1997</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2578,7 +2578,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>78,52%</t>
+          <t>73,62%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2628,7 +2628,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>826</t>
+          <t>817</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -2643,7 +2643,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2823,7 +2823,7 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5643</t>
+          <t>5917</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>55,78%</t>
+          <t>58,49%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2858,7 +2858,7 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>8057</t>
+          <t>8212</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
@@ -2873,7 +2873,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>61,47%</t>
+          <t>62,65%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -2941,7 +2941,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>4473</t>
+          <t>4199</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2956,7 +2956,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>44,22%</t>
+          <t>41,51%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5050</t>
+          <t>4895</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>38,53%</t>
+          <t>37,35%</t>
         </is>
       </c>
     </row>
@@ -3131,12 +3131,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3214</t>
+          <t>2929</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7448</t>
+          <t>7499</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3146,12 +3146,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>34,01%</t>
+          <t>31,0%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>78,81%</t>
+          <t>79,36%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>7521</t>
+          <t>7580</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>14736</t>
+          <t>15077</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3181,12 +3181,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>41,2%</t>
+          <t>41,53%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>80,73%</t>
+          <t>82,6%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>12757</t>
+          <t>12144</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>21418</t>
+          <t>21346</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>46,05%</t>
+          <t>43,84%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>77,31%</t>
+          <t>77,05%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>1951</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>6236</t>
+          <t>6521</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>65,99%</t>
+          <t>69,0%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3517</t>
+          <t>3176</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>10732</t>
+          <t>10673</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>58,8%</t>
+          <t>58,47%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>6357</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>14946</t>
+          <t>15559</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>53,95%</t>
+          <t>56,16%</t>
         </is>
       </c>
     </row>
